--- a/Result/profitability/1612.xlsx
+++ b/Result/profitability/1612.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5975</v>
+        <v>0.7675</v>
       </c>
       <c r="N2" t="n">
-        <v>14.15</v>
+        <v>14.43625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.55875</v>
+        <v>0.72625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.56875</v>
+        <v>13.665</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5175</v>
+        <v>0.6675</v>
       </c>
       <c r="N4" t="n">
-        <v>12.78625</v>
+        <v>12.77875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.40125</v>
+        <v>0.5137499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>10.61625</v>
+        <v>10.76875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.31125</v>
+        <v>0.44875</v>
       </c>
       <c r="N6" t="n">
-        <v>9.74625</v>
+        <v>10.0225</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.23</v>
+        <v>0.3825</v>
       </c>
       <c r="N7" t="n">
-        <v>8.793749999999999</v>
+        <v>8.675000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1875</v>
+        <v>0.31</v>
       </c>
       <c r="N8" t="n">
-        <v>7.36</v>
+        <v>7.1325</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.11625</v>
       </c>
       <c r="N10" t="n">
-        <v>5.768750000000001</v>
+        <v>5.76875</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1612</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2052</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1733</v>
+      </c>
+      <c r="E75" t="n">
+        <v>320</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>234</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.40%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>389</v>
+      </c>
+      <c r="J75" t="n">
+        <v>623</v>
+      </c>
+      <c r="K75" t="n">
+        <v>568</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.1225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.195121951219512</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.819999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1045977011494252</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.220000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08495821727019504</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
